--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247514</v>
+        <v>113247529</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535573</v>
+        <v>535707</v>
       </c>
       <c r="R2" t="n">
-        <v>7200154</v>
+        <v>7200224</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247575</v>
+        <v>113247512</v>
       </c>
       <c r="B3" t="n">
-        <v>77508</v>
+        <v>56765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535617</v>
+        <v>535629</v>
       </c>
       <c r="R3" t="n">
-        <v>7200220</v>
+        <v>7200142</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247557</v>
+        <v>113247555</v>
       </c>
       <c r="B4" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535823</v>
+        <v>535620</v>
       </c>
       <c r="R4" t="n">
-        <v>7200325</v>
+        <v>7200220</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247512</v>
+        <v>113247575</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>77524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535629</v>
+        <v>535617</v>
       </c>
       <c r="R5" t="n">
-        <v>7200142</v>
+        <v>7200220</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247529</v>
+        <v>113247557</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535707</v>
+        <v>535823</v>
       </c>
       <c r="R6" t="n">
-        <v>7200224</v>
+        <v>7200325</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247555</v>
+        <v>113247574</v>
       </c>
       <c r="B7" t="n">
-        <v>78105</v>
+        <v>77098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,7 +1283,7 @@
         <v>535620</v>
       </c>
       <c r="R7" t="n">
-        <v>7200220</v>
+        <v>7200222</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247531</v>
+        <v>113247515</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>56765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535838</v>
+        <v>535739</v>
       </c>
       <c r="R8" t="n">
-        <v>7200343</v>
+        <v>7200231</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247574</v>
+        <v>113247540</v>
       </c>
       <c r="B9" t="n">
-        <v>77082</v>
+        <v>79118</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535620</v>
+        <v>535824</v>
       </c>
       <c r="R9" t="n">
-        <v>7200222</v>
+        <v>7200325</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247515</v>
+        <v>113247531</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535739</v>
+        <v>535838</v>
       </c>
       <c r="R10" t="n">
-        <v>7200231</v>
+        <v>7200343</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247513</v>
+        <v>113247514</v>
       </c>
       <c r="B11" t="n">
         <v>56765</v>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535575</v>
+        <v>535573</v>
       </c>
       <c r="R11" t="n">
-        <v>7200140</v>
+        <v>7200154</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247540</v>
+        <v>113247513</v>
       </c>
       <c r="B12" t="n">
-        <v>79102</v>
+        <v>56765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,38 +1822,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535824</v>
+        <v>535575</v>
       </c>
       <c r="R12" t="n">
-        <v>7200325</v>
+        <v>7200140</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247529</v>
+        <v>113247555</v>
       </c>
       <c r="B2" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535707</v>
+        <v>535620</v>
       </c>
       <c r="R2" t="n">
-        <v>7200224</v>
+        <v>7200220</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247512</v>
+        <v>113247575</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>77524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535629</v>
+        <v>535617</v>
       </c>
       <c r="R3" t="n">
-        <v>7200142</v>
+        <v>7200220</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247555</v>
+        <v>113247529</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535620</v>
+        <v>535707</v>
       </c>
       <c r="R4" t="n">
-        <v>7200220</v>
+        <v>7200224</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247575</v>
+        <v>113247512</v>
       </c>
       <c r="B5" t="n">
-        <v>77524</v>
+        <v>56765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535617</v>
+        <v>535629</v>
       </c>
       <c r="R5" t="n">
-        <v>7200220</v>
+        <v>7200142</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247555</v>
+        <v>113247512</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535620</v>
+        <v>535629</v>
       </c>
       <c r="R2" t="n">
-        <v>7200220</v>
+        <v>7200142</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247575</v>
+        <v>113247515</v>
       </c>
       <c r="B3" t="n">
-        <v>77524</v>
+        <v>56765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535617</v>
+        <v>535739</v>
       </c>
       <c r="R3" t="n">
-        <v>7200220</v>
+        <v>7200231</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247529</v>
+        <v>113247557</v>
       </c>
       <c r="B4" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535707</v>
+        <v>535823</v>
       </c>
       <c r="R4" t="n">
-        <v>7200224</v>
+        <v>7200325</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247512</v>
+        <v>113247513</v>
       </c>
       <c r="B5" t="n">
         <v>56765</v>
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535629</v>
+        <v>535575</v>
       </c>
       <c r="R5" t="n">
-        <v>7200142</v>
+        <v>7200140</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247557</v>
+        <v>113247531</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535823</v>
+        <v>535838</v>
       </c>
       <c r="R6" t="n">
-        <v>7200325</v>
+        <v>7200343</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247515</v>
+        <v>113247514</v>
       </c>
       <c r="B8" t="n">
         <v>56765</v>
@@ -1397,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535739</v>
+        <v>535573</v>
       </c>
       <c r="R8" t="n">
-        <v>7200231</v>
+        <v>7200154</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247540</v>
+        <v>113247529</v>
       </c>
       <c r="B9" t="n">
-        <v>79118</v>
+        <v>79185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535824</v>
+        <v>535707</v>
       </c>
       <c r="R9" t="n">
-        <v>7200325</v>
+        <v>7200224</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247531</v>
+        <v>113247575</v>
       </c>
       <c r="B10" t="n">
-        <v>79185</v>
+        <v>77524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535838</v>
+        <v>535617</v>
       </c>
       <c r="R10" t="n">
-        <v>7200343</v>
+        <v>7200220</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247514</v>
+        <v>113247555</v>
       </c>
       <c r="B11" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535573</v>
+        <v>535620</v>
       </c>
       <c r="R11" t="n">
-        <v>7200154</v>
+        <v>7200220</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247513</v>
+        <v>113247540</v>
       </c>
       <c r="B12" t="n">
-        <v>56765</v>
+        <v>79118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,43 +1827,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535575</v>
+        <v>535824</v>
       </c>
       <c r="R12" t="n">
-        <v>7200140</v>
+        <v>7200325</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247512</v>
+        <v>113247515</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535629</v>
+        <v>535739</v>
       </c>
       <c r="R2" t="n">
-        <v>7200142</v>
+        <v>7200231</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247515</v>
+        <v>113247540</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>79130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535739</v>
+        <v>535824</v>
       </c>
       <c r="R3" t="n">
-        <v>7200231</v>
+        <v>7200325</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247557</v>
+        <v>113247555</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535823</v>
+        <v>535620</v>
       </c>
       <c r="R4" t="n">
-        <v>7200325</v>
+        <v>7200220</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247513</v>
+        <v>113247514</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535575</v>
+        <v>535573</v>
       </c>
       <c r="R5" t="n">
-        <v>7200140</v>
+        <v>7200154</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247531</v>
+        <v>113247557</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535838</v>
+        <v>535823</v>
       </c>
       <c r="R6" t="n">
-        <v>7200343</v>
+        <v>7200325</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247574</v>
+        <v>113247512</v>
       </c>
       <c r="B7" t="n">
-        <v>77098</v>
+        <v>56766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535620</v>
+        <v>535629</v>
       </c>
       <c r="R7" t="n">
-        <v>7200222</v>
+        <v>7200142</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247514</v>
+        <v>113247513</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535573</v>
+        <v>535575</v>
       </c>
       <c r="R8" t="n">
-        <v>7200154</v>
+        <v>7200140</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1482,7 @@
         <v>113247529</v>
       </c>
       <c r="B9" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247575</v>
+        <v>113247531</v>
       </c>
       <c r="B10" t="n">
-        <v>77524</v>
+        <v>79197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535617</v>
+        <v>535838</v>
       </c>
       <c r="R10" t="n">
-        <v>7200220</v>
+        <v>7200343</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247555</v>
+        <v>113247575</v>
       </c>
       <c r="B11" t="n">
-        <v>78121</v>
+        <v>77536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535620</v>
+        <v>535617</v>
       </c>
       <c r="R11" t="n">
         <v>7200220</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247540</v>
+        <v>113247574</v>
       </c>
       <c r="B12" t="n">
-        <v>79118</v>
+        <v>77110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535824</v>
+        <v>535620</v>
       </c>
       <c r="R12" t="n">
-        <v>7200325</v>
+        <v>7200222</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247515</v>
+        <v>113247529</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535739</v>
+        <v>535707</v>
       </c>
       <c r="R2" t="n">
-        <v>7200231</v>
+        <v>7200224</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247540</v>
+        <v>113247557</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535824</v>
+        <v>535823</v>
       </c>
       <c r="R3" t="n">
         <v>7200325</v>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247555</v>
+        <v>113247574</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>77110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,7 +942,7 @@
         <v>535620</v>
       </c>
       <c r="R4" t="n">
-        <v>7200220</v>
+        <v>7200222</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247514</v>
+        <v>113247555</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535573</v>
+        <v>535620</v>
       </c>
       <c r="R5" t="n">
-        <v>7200154</v>
+        <v>7200220</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247557</v>
+        <v>113247540</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>79130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,7 +1163,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535823</v>
+        <v>535824</v>
       </c>
       <c r="R6" t="n">
         <v>7200325</v>
@@ -1245,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247512</v>
+        <v>113247514</v>
       </c>
       <c r="B7" t="n">
         <v>56766</v>
@@ -1290,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535629</v>
+        <v>535573</v>
       </c>
       <c r="R7" t="n">
-        <v>7200142</v>
+        <v>7200154</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247513</v>
+        <v>113247515</v>
       </c>
       <c r="B8" t="n">
         <v>56766</v>
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535575</v>
+        <v>535739</v>
       </c>
       <c r="R8" t="n">
-        <v>7200140</v>
+        <v>7200231</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247529</v>
+        <v>113247575</v>
       </c>
       <c r="B9" t="n">
-        <v>79197</v>
+        <v>77536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535707</v>
+        <v>535617</v>
       </c>
       <c r="R9" t="n">
-        <v>7200224</v>
+        <v>7200220</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247575</v>
+        <v>113247513</v>
       </c>
       <c r="B11" t="n">
-        <v>77536</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535617</v>
+        <v>535575</v>
       </c>
       <c r="R11" t="n">
-        <v>7200220</v>
+        <v>7200140</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247574</v>
+        <v>113247512</v>
       </c>
       <c r="B12" t="n">
-        <v>77110</v>
+        <v>56766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535620</v>
+        <v>535629</v>
       </c>
       <c r="R12" t="n">
-        <v>7200222</v>
+        <v>7200142</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113247529</v>
       </c>
       <c r="B2" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247557</v>
+        <v>113247513</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535823</v>
+        <v>535575</v>
       </c>
       <c r="R3" t="n">
-        <v>7200325</v>
+        <v>7200140</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247574</v>
+        <v>113247514</v>
       </c>
       <c r="B4" t="n">
-        <v>77110</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535620</v>
+        <v>535573</v>
       </c>
       <c r="R4" t="n">
-        <v>7200222</v>
+        <v>7200154</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247555</v>
+        <v>113247540</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>79152</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535620</v>
+        <v>535824</v>
       </c>
       <c r="R5" t="n">
-        <v>7200220</v>
+        <v>7200325</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247540</v>
+        <v>113247555</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>78155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535824</v>
+        <v>535620</v>
       </c>
       <c r="R6" t="n">
-        <v>7200325</v>
+        <v>7200220</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247514</v>
+        <v>113247515</v>
       </c>
       <c r="B7" t="n">
         <v>56766</v>
@@ -1280,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535573</v>
+        <v>535739</v>
       </c>
       <c r="R7" t="n">
-        <v>7200154</v>
+        <v>7200231</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247515</v>
+        <v>113247557</v>
       </c>
       <c r="B8" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535739</v>
+        <v>535823</v>
       </c>
       <c r="R8" t="n">
-        <v>7200231</v>
+        <v>7200325</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1477,7 @@
         <v>113247575</v>
       </c>
       <c r="B9" t="n">
-        <v>77536</v>
+        <v>77558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247531</v>
+        <v>113247512</v>
       </c>
       <c r="B10" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535838</v>
+        <v>535629</v>
       </c>
       <c r="R10" t="n">
-        <v>7200343</v>
+        <v>7200142</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247513</v>
+        <v>113247531</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>79219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535575</v>
+        <v>535838</v>
       </c>
       <c r="R11" t="n">
-        <v>7200140</v>
+        <v>7200343</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247512</v>
+        <v>113247574</v>
       </c>
       <c r="B12" t="n">
-        <v>56766</v>
+        <v>77132</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535629</v>
+        <v>535620</v>
       </c>
       <c r="R12" t="n">
-        <v>7200142</v>
+        <v>7200222</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247529</v>
+        <v>113247514</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>56769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535707</v>
+        <v>535573</v>
       </c>
       <c r="R2" t="n">
-        <v>7200224</v>
+        <v>7200154</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247513</v>
+        <v>113247557</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535575</v>
+        <v>535823</v>
       </c>
       <c r="R3" t="n">
-        <v>7200140</v>
+        <v>7200325</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247514</v>
+        <v>113247513</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535573</v>
+        <v>535575</v>
       </c>
       <c r="R4" t="n">
-        <v>7200154</v>
+        <v>7200140</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>113247540</v>
       </c>
       <c r="B5" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247555</v>
+        <v>113247531</v>
       </c>
       <c r="B6" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535620</v>
+        <v>535838</v>
       </c>
       <c r="R6" t="n">
-        <v>7200220</v>
+        <v>7200343</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247515</v>
+        <v>113247575</v>
       </c>
       <c r="B7" t="n">
-        <v>56766</v>
+        <v>77561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535739</v>
+        <v>535617</v>
       </c>
       <c r="R7" t="n">
-        <v>7200231</v>
+        <v>7200220</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247557</v>
+        <v>113247529</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535823</v>
+        <v>535707</v>
       </c>
       <c r="R8" t="n">
-        <v>7200325</v>
+        <v>7200224</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247575</v>
+        <v>113247512</v>
       </c>
       <c r="B9" t="n">
-        <v>77558</v>
+        <v>56769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535617</v>
+        <v>535629</v>
       </c>
       <c r="R9" t="n">
-        <v>7200220</v>
+        <v>7200142</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247512</v>
+        <v>113247555</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535629</v>
+        <v>535620</v>
       </c>
       <c r="R10" t="n">
-        <v>7200142</v>
+        <v>7200220</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247531</v>
+        <v>113247515</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>56769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535838</v>
+        <v>535739</v>
       </c>
       <c r="R11" t="n">
-        <v>7200343</v>
+        <v>7200231</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
         <v>113247574</v>
       </c>
       <c r="B12" t="n">
-        <v>77132</v>
+        <v>77135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247557</v>
+        <v>113247513</v>
       </c>
       <c r="B3" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535823</v>
+        <v>535575</v>
       </c>
       <c r="R3" t="n">
-        <v>7200325</v>
+        <v>7200140</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247513</v>
+        <v>113247529</v>
       </c>
       <c r="B4" t="n">
-        <v>56769</v>
+        <v>79223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535575</v>
+        <v>535707</v>
       </c>
       <c r="R4" t="n">
-        <v>7200140</v>
+        <v>7200224</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247540</v>
+        <v>113247574</v>
       </c>
       <c r="B5" t="n">
-        <v>79156</v>
+        <v>77135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535824</v>
+        <v>535620</v>
       </c>
       <c r="R5" t="n">
-        <v>7200325</v>
+        <v>7200222</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247531</v>
+        <v>113247575</v>
       </c>
       <c r="B6" t="n">
-        <v>79223</v>
+        <v>77561</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535838</v>
+        <v>535617</v>
       </c>
       <c r="R6" t="n">
-        <v>7200343</v>
+        <v>7200220</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247575</v>
+        <v>113247557</v>
       </c>
       <c r="B7" t="n">
-        <v>77561</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535617</v>
+        <v>535823</v>
       </c>
       <c r="R7" t="n">
-        <v>7200220</v>
+        <v>7200325</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247529</v>
+        <v>113247555</v>
       </c>
       <c r="B8" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535707</v>
+        <v>535620</v>
       </c>
       <c r="R8" t="n">
-        <v>7200224</v>
+        <v>7200220</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247512</v>
+        <v>113247531</v>
       </c>
       <c r="B9" t="n">
-        <v>56769</v>
+        <v>79223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535629</v>
+        <v>535838</v>
       </c>
       <c r="R9" t="n">
-        <v>7200142</v>
+        <v>7200343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247555</v>
+        <v>113247540</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>79156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535620</v>
+        <v>535824</v>
       </c>
       <c r="R10" t="n">
-        <v>7200220</v>
+        <v>7200325</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247515</v>
+        <v>113247512</v>
       </c>
       <c r="B11" t="n">
         <v>56769</v>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535739</v>
+        <v>535629</v>
       </c>
       <c r="R11" t="n">
-        <v>7200231</v>
+        <v>7200142</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247574</v>
+        <v>113247515</v>
       </c>
       <c r="B12" t="n">
-        <v>77135</v>
+        <v>56769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535620</v>
+        <v>535739</v>
       </c>
       <c r="R12" t="n">
-        <v>7200222</v>
+        <v>7200231</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247514</v>
+        <v>113247529</v>
       </c>
       <c r="B2" t="n">
-        <v>56769</v>
+        <v>79229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535573</v>
+        <v>535707</v>
       </c>
       <c r="R2" t="n">
-        <v>7200154</v>
+        <v>7200224</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247513</v>
+        <v>113247531</v>
       </c>
       <c r="B3" t="n">
-        <v>56769</v>
+        <v>79229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535575</v>
+        <v>535838</v>
       </c>
       <c r="R3" t="n">
-        <v>7200140</v>
+        <v>7200343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247529</v>
+        <v>113247575</v>
       </c>
       <c r="B4" t="n">
-        <v>79223</v>
+        <v>77567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535707</v>
+        <v>535617</v>
       </c>
       <c r="R4" t="n">
-        <v>7200224</v>
+        <v>7200220</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1014,7 @@
         <v>113247574</v>
       </c>
       <c r="B5" t="n">
-        <v>77135</v>
+        <v>77141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247575</v>
+        <v>113247540</v>
       </c>
       <c r="B6" t="n">
-        <v>77561</v>
+        <v>79162</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535617</v>
+        <v>535824</v>
       </c>
       <c r="R6" t="n">
-        <v>7200220</v>
+        <v>7200325</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247557</v>
+        <v>113247555</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535823</v>
+        <v>535620</v>
       </c>
       <c r="R7" t="n">
-        <v>7200325</v>
+        <v>7200220</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247555</v>
+        <v>113247557</v>
       </c>
       <c r="B8" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535620</v>
+        <v>535823</v>
       </c>
       <c r="R8" t="n">
-        <v>7200220</v>
+        <v>7200325</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247531</v>
+        <v>113247513</v>
       </c>
       <c r="B9" t="n">
-        <v>79223</v>
+        <v>56773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535838</v>
+        <v>535575</v>
       </c>
       <c r="R9" t="n">
-        <v>7200343</v>
+        <v>7200140</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247540</v>
+        <v>113247515</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>56773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,38 +1588,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535824</v>
+        <v>535739</v>
       </c>
       <c r="R10" t="n">
-        <v>7200325</v>
+        <v>7200231</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
         <v>113247512</v>
       </c>
       <c r="B11" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247515</v>
+        <v>113247514</v>
       </c>
       <c r="B12" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535739</v>
+        <v>535573</v>
       </c>
       <c r="R12" t="n">
-        <v>7200231</v>
+        <v>7200154</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247529</v>
+        <v>113247575</v>
       </c>
       <c r="B2" t="n">
-        <v>79229</v>
+        <v>77567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535707</v>
+        <v>535617</v>
       </c>
       <c r="R2" t="n">
-        <v>7200224</v>
+        <v>7200220</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247531</v>
+        <v>113247555</v>
       </c>
       <c r="B3" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535838</v>
+        <v>535620</v>
       </c>
       <c r="R3" t="n">
-        <v>7200343</v>
+        <v>7200220</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247575</v>
+        <v>113247514</v>
       </c>
       <c r="B4" t="n">
-        <v>77567</v>
+        <v>56773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535617</v>
+        <v>535573</v>
       </c>
       <c r="R4" t="n">
-        <v>7200220</v>
+        <v>7200154</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247574</v>
+        <v>113247515</v>
       </c>
       <c r="B5" t="n">
-        <v>77141</v>
+        <v>56773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535620</v>
+        <v>535739</v>
       </c>
       <c r="R5" t="n">
-        <v>7200222</v>
+        <v>7200231</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247540</v>
+        <v>113247512</v>
       </c>
       <c r="B6" t="n">
-        <v>79162</v>
+        <v>56773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1145,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535824</v>
+        <v>535629</v>
       </c>
       <c r="R6" t="n">
-        <v>7200325</v>
+        <v>7200142</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247555</v>
+        <v>113247529</v>
       </c>
       <c r="B7" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535620</v>
+        <v>535707</v>
       </c>
       <c r="R7" t="n">
-        <v>7200220</v>
+        <v>7200224</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247557</v>
+        <v>113247531</v>
       </c>
       <c r="B8" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535823</v>
+        <v>535838</v>
       </c>
       <c r="R8" t="n">
-        <v>7200325</v>
+        <v>7200343</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247515</v>
+        <v>113247557</v>
       </c>
       <c r="B10" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535739</v>
+        <v>535823</v>
       </c>
       <c r="R10" t="n">
-        <v>7200231</v>
+        <v>7200325</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247512</v>
+        <v>113247540</v>
       </c>
       <c r="B11" t="n">
-        <v>56773</v>
+        <v>79162</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,43 +1715,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535629</v>
+        <v>535824</v>
       </c>
       <c r="R11" t="n">
-        <v>7200142</v>
+        <v>7200325</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247514</v>
+        <v>113247574</v>
       </c>
       <c r="B12" t="n">
-        <v>56773</v>
+        <v>77141</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535573</v>
+        <v>535620</v>
       </c>
       <c r="R12" t="n">
-        <v>7200154</v>
+        <v>7200222</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113247575</v>
       </c>
       <c r="B2" t="n">
-        <v>77567</v>
+        <v>77574</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247555</v>
+        <v>113247513</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>56780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535620</v>
+        <v>535575</v>
       </c>
       <c r="R3" t="n">
-        <v>7200220</v>
+        <v>7200140</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247514</v>
+        <v>113247555</v>
       </c>
       <c r="B4" t="n">
-        <v>56773</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535573</v>
+        <v>535620</v>
       </c>
       <c r="R4" t="n">
-        <v>7200154</v>
+        <v>7200220</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1019,7 @@
         <v>113247515</v>
       </c>
       <c r="B5" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>113247512</v>
       </c>
       <c r="B6" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247529</v>
+        <v>113247514</v>
       </c>
       <c r="B7" t="n">
-        <v>79229</v>
+        <v>56780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535707</v>
+        <v>535573</v>
       </c>
       <c r="R7" t="n">
-        <v>7200224</v>
+        <v>7200154</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1370,7 @@
         <v>113247531</v>
       </c>
       <c r="B8" t="n">
-        <v>79229</v>
+        <v>79236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247513</v>
+        <v>113247529</v>
       </c>
       <c r="B9" t="n">
-        <v>56773</v>
+        <v>79236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535575</v>
+        <v>535707</v>
       </c>
       <c r="R9" t="n">
-        <v>7200140</v>
+        <v>7200224</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247557</v>
+        <v>113247574</v>
       </c>
       <c r="B10" t="n">
-        <v>78164</v>
+        <v>77148</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535823</v>
+        <v>535620</v>
       </c>
       <c r="R10" t="n">
-        <v>7200325</v>
+        <v>7200222</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247540</v>
+        <v>113247557</v>
       </c>
       <c r="B11" t="n">
-        <v>79162</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,25 +1715,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535824</v>
+        <v>535823</v>
       </c>
       <c r="R11" t="n">
         <v>7200325</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247574</v>
+        <v>113247540</v>
       </c>
       <c r="B12" t="n">
-        <v>77141</v>
+        <v>79169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535620</v>
+        <v>535824</v>
       </c>
       <c r="R12" t="n">
-        <v>7200222</v>
+        <v>7200325</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49135-2023 artfynd.xlsx
+++ b/artfynd/A 49135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113247529</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247540</v>
+        <v>113247531</v>
       </c>
       <c r="B3" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535824</v>
+        <v>535838</v>
       </c>
       <c r="R3" t="n">
-        <v>7200325</v>
+        <v>7200343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247575</v>
+        <v>113247532</v>
       </c>
       <c r="B4" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535618</v>
+        <v>535864</v>
       </c>
       <c r="R4" t="n">
-        <v>7200220</v>
+        <v>7200393</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247531</v>
+        <v>120461288</v>
       </c>
       <c r="B5" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535838</v>
+        <v>535753</v>
       </c>
       <c r="R5" t="n">
-        <v>7200343</v>
+        <v>7200057</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,55 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247514</v>
+        <v>120461285</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535573</v>
+        <v>535708</v>
       </c>
       <c r="R6" t="n">
-        <v>7200153</v>
+        <v>7200064</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247513</v>
+        <v>113247554</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535576</v>
+        <v>535750</v>
       </c>
       <c r="R7" t="n">
-        <v>7200140</v>
+        <v>7200133</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,16 +1320,11 @@
         <v>113247555</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1469,55 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247512</v>
+        <v>113247556</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535628</v>
+        <v>535746</v>
       </c>
       <c r="R9" t="n">
-        <v>7200141</v>
+        <v>7200290</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,16 +1534,11 @@
         <v>113247557</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1698,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247515</v>
+        <v>113247575</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535739</v>
+        <v>535618</v>
       </c>
       <c r="R11" t="n">
-        <v>7200231</v>
+        <v>7200220</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247574</v>
+        <v>113247540</v>
       </c>
       <c r="B12" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535620</v>
+        <v>535824</v>
       </c>
       <c r="R12" t="n">
-        <v>7200222</v>
+        <v>7200325</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,6 +1849,1004 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113247574</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>535620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7200222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113247511</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>535752</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7200129</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113247512</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>535628</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7200141</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113247513</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>535576</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7200140</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113247514</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>535573</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7200153</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113247515</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>535739</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7200231</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113247516</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>535746</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7200285</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120286826</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Koksikoppen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535769</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7200054</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>David Magnusson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120461286</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535762</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7200051</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
